--- a/output/yearly_population_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_65_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5269</v>
+        <v>7534</v>
       </c>
       <c r="C2" t="n">
-        <v>4000</v>
+        <v>6039</v>
       </c>
       <c r="D2" t="n">
-        <v>16436</v>
+        <v>30411</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>3844</v>
       </c>
       <c r="C3" t="n">
-        <v>4669</v>
+        <v>5563</v>
       </c>
       <c r="D3" t="n">
-        <v>11029</v>
+        <v>14752</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="C4" t="n">
-        <v>4721</v>
+        <v>5566</v>
       </c>
       <c r="D4" t="n">
-        <v>4969</v>
+        <v>8407</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1957</v>
+        <v>1831</v>
       </c>
       <c r="C5" t="n">
-        <v>3356</v>
+        <v>4018</v>
       </c>
       <c r="D5" t="n">
-        <v>1888</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="C6" t="n">
-        <v>2665</v>
+        <v>2845</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>1715</v>
+        <v>1973</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>848</v>
+        <v>1012</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
         <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6518</v>
+        <v>7333</v>
       </c>
       <c r="C2" t="n">
-        <v>12776</v>
+        <v>7809</v>
       </c>
       <c r="D2" t="n">
-        <v>16396</v>
+        <v>34116</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3537</v>
+        <v>4403</v>
       </c>
       <c r="C3" t="n">
-        <v>3815</v>
+        <v>5090</v>
       </c>
       <c r="D3" t="n">
-        <v>11048</v>
+        <v>15890</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2812</v>
+        <v>2908</v>
       </c>
       <c r="C4" t="n">
-        <v>4551</v>
+        <v>5448</v>
       </c>
       <c r="D4" t="n">
-        <v>5865</v>
+        <v>9186</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2146</v>
+        <v>2049</v>
       </c>
       <c r="C5" t="n">
-        <v>3954</v>
+        <v>4594</v>
       </c>
       <c r="D5" t="n">
-        <v>2315</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1314</v>
+        <v>1233</v>
       </c>
       <c r="C6" t="n">
-        <v>2936</v>
+        <v>3335</v>
       </c>
       <c r="D6" t="n">
-        <v>1094</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="C7" t="n">
-        <v>2161</v>
+        <v>2328</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>1230</v>
+        <v>1406</v>
       </c>
       <c r="D8" t="n">
         <v>463</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10260</v>
+        <v>7653</v>
       </c>
       <c r="C2" t="n">
-        <v>10173</v>
+        <v>10570</v>
       </c>
       <c r="D2" t="n">
-        <v>16140</v>
+        <v>29568</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3893</v>
+        <v>4533</v>
       </c>
       <c r="C3" t="n">
-        <v>6810</v>
+        <v>5547</v>
       </c>
       <c r="D3" t="n">
-        <v>11007</v>
+        <v>17060</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2666</v>
+        <v>2973</v>
       </c>
       <c r="C4" t="n">
-        <v>4073</v>
+        <v>5131</v>
       </c>
       <c r="D4" t="n">
-        <v>6426</v>
+        <v>9783</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2163</v>
+        <v>2122</v>
       </c>
       <c r="C5" t="n">
-        <v>4141</v>
+        <v>4806</v>
       </c>
       <c r="D5" t="n">
-        <v>2789</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1530</v>
+        <v>1414</v>
       </c>
       <c r="C6" t="n">
-        <v>3319</v>
+        <v>3813</v>
       </c>
       <c r="D6" t="n">
-        <v>1244</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>835</v>
+        <v>776</v>
       </c>
       <c r="C7" t="n">
-        <v>2494</v>
+        <v>2698</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="C8" t="n">
-        <v>1600</v>
+        <v>1744</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>842</v>
+        <v>938</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8981</v>
+        <v>7135</v>
       </c>
       <c r="C2" t="n">
-        <v>6673</v>
+        <v>7272</v>
       </c>
       <c r="D2" t="n">
-        <v>13205</v>
+        <v>24473</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4825</v>
+        <v>5390</v>
       </c>
       <c r="C3" t="n">
-        <v>9566</v>
+        <v>8627</v>
       </c>
       <c r="D3" t="n">
-        <v>12185</v>
+        <v>18564</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1998</v>
+        <v>1960</v>
       </c>
       <c r="C4" t="n">
-        <v>6321</v>
+        <v>7421</v>
       </c>
       <c r="D4" t="n">
-        <v>6157</v>
+        <v>9630</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1413</v>
+        <v>1306</v>
       </c>
       <c r="C5" t="n">
-        <v>3252</v>
+        <v>3736</v>
       </c>
       <c r="D5" t="n">
-        <v>1995</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>771</v>
+        <v>717</v>
       </c>
       <c r="C6" t="n">
-        <v>2444</v>
+        <v>2644</v>
       </c>
       <c r="D6" t="n">
-        <v>708</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>1568</v>
+        <v>1709</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>825</v>
+        <v>919</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>4304</v>
       </c>
       <c r="C2" t="n">
-        <v>3057</v>
+        <v>3588</v>
       </c>
       <c r="D2" t="n">
-        <v>9391</v>
+        <v>17995</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5648</v>
+        <v>5314</v>
       </c>
       <c r="C3" t="n">
-        <v>7382</v>
+        <v>7273</v>
       </c>
       <c r="D3" t="n">
-        <v>11727</v>
+        <v>18476</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2722</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>8021</v>
+        <v>8107</v>
       </c>
       <c r="D4" t="n">
-        <v>6954</v>
+        <v>10716</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>1467</v>
       </c>
       <c r="C5" t="n">
-        <v>4666</v>
+        <v>5323</v>
       </c>
       <c r="D5" t="n">
-        <v>2532</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>941</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>2862</v>
+        <v>3146</v>
       </c>
       <c r="D6" t="n">
-        <v>862</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>2106</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5901</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="n">
-        <v>8656</v>
+        <v>6835</v>
       </c>
       <c r="D2" t="n">
-        <v>18290</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4564</v>
+        <v>4117</v>
       </c>
       <c r="C3" t="n">
-        <v>4580</v>
+        <v>4885</v>
       </c>
       <c r="D3" t="n">
-        <v>10583</v>
+        <v>17168</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3485</v>
+        <v>3342</v>
       </c>
       <c r="C4" t="n">
-        <v>7599</v>
+        <v>7530</v>
       </c>
       <c r="D4" t="n">
-        <v>7567</v>
+        <v>11656</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1849</v>
+        <v>1791</v>
       </c>
       <c r="C5" t="n">
-        <v>6211</v>
+        <v>6572</v>
       </c>
       <c r="D5" t="n">
-        <v>3176</v>
+        <v>4856</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>1011</v>
       </c>
       <c r="C6" t="n">
-        <v>3709</v>
+        <v>4077</v>
       </c>
       <c r="D6" t="n">
-        <v>1106</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>452</v>
       </c>
       <c r="C7" t="n">
-        <v>2367</v>
+        <v>2574</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1483</v>
+        <v>1558</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3413</v>
+        <v>2828</v>
       </c>
       <c r="C2" t="n">
-        <v>3853</v>
+        <v>3204</v>
       </c>
       <c r="D2" t="n">
-        <v>12644</v>
+        <v>11584</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4729</v>
+        <v>4158</v>
       </c>
       <c r="C3" t="n">
-        <v>5886</v>
+        <v>5391</v>
       </c>
       <c r="D3" t="n">
-        <v>11192</v>
+        <v>16716</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3898</v>
+        <v>3634</v>
       </c>
       <c r="C4" t="n">
-        <v>7171</v>
+        <v>7232</v>
       </c>
       <c r="D4" t="n">
-        <v>7989</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1961</v>
+        <v>1847</v>
       </c>
       <c r="C5" t="n">
-        <v>7345</v>
+        <v>7823</v>
       </c>
       <c r="D5" t="n">
-        <v>3447</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>828</v>
       </c>
       <c r="C6" t="n">
-        <v>4698</v>
+        <v>4903</v>
       </c>
       <c r="D6" t="n">
-        <v>1105</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2597</v>
+        <v>2743</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1176</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4557</v>
+        <v>3623</v>
       </c>
       <c r="C2" t="n">
-        <v>5196</v>
+        <v>5248</v>
       </c>
       <c r="D2" t="n">
-        <v>14295</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3551</v>
+        <v>3088</v>
       </c>
       <c r="C3" t="n">
-        <v>4345</v>
+        <v>3921</v>
       </c>
       <c r="D3" t="n">
-        <v>10738</v>
+        <v>15055</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3711</v>
+        <v>3363</v>
       </c>
       <c r="C4" t="n">
-        <v>6449</v>
+        <v>6284</v>
       </c>
       <c r="D4" t="n">
-        <v>8268</v>
+        <v>12672</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2457</v>
+        <v>2292</v>
       </c>
       <c r="C5" t="n">
-        <v>7180</v>
+        <v>7399</v>
       </c>
       <c r="D5" t="n">
-        <v>4039</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>5867</v>
+        <v>6187</v>
       </c>
       <c r="D6" t="n">
-        <v>1427</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>3532</v>
+        <v>3615</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1741</v>
+        <v>1773</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3169</v>
+        <v>2675</v>
       </c>
       <c r="C2" t="n">
-        <v>3376</v>
+        <v>2784</v>
       </c>
       <c r="D2" t="n">
-        <v>10273</v>
+        <v>13806</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3406</v>
+        <v>2856</v>
       </c>
       <c r="C3" t="n">
-        <v>4289</v>
+        <v>4030</v>
       </c>
       <c r="D3" t="n">
-        <v>10695</v>
+        <v>14625</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3371</v>
+        <v>3024</v>
       </c>
       <c r="C4" t="n">
-        <v>5549</v>
+        <v>5381</v>
       </c>
       <c r="D4" t="n">
-        <v>8427</v>
+        <v>12850</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2688</v>
+        <v>2472</v>
       </c>
       <c r="C5" t="n">
-        <v>7025</v>
+        <v>7062</v>
       </c>
       <c r="D5" t="n">
-        <v>4442</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>1302</v>
       </c>
       <c r="C6" t="n">
-        <v>6540</v>
+        <v>6820</v>
       </c>
       <c r="D6" t="n">
-        <v>1702</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>4390</v>
+        <v>4491</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2228</v>
+        <v>2264</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>756</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4929</v>
+        <v>3664</v>
       </c>
       <c r="C2" t="n">
-        <v>4131</v>
+        <v>6501</v>
       </c>
       <c r="D2" t="n">
-        <v>10431</v>
+        <v>15268</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2762</v>
+        <v>2349</v>
       </c>
       <c r="C3" t="n">
-        <v>3492</v>
+        <v>3146</v>
       </c>
       <c r="D3" t="n">
-        <v>9939</v>
+        <v>13590</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2969</v>
+        <v>2602</v>
       </c>
       <c r="C4" t="n">
-        <v>4877</v>
+        <v>4698</v>
       </c>
       <c r="D4" t="n">
-        <v>8519</v>
+        <v>12714</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2669</v>
+        <v>2426</v>
       </c>
       <c r="C5" t="n">
-        <v>6255</v>
+        <v>6237</v>
       </c>
       <c r="D5" t="n">
-        <v>4880</v>
+        <v>7223</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1777</v>
+        <v>1574</v>
       </c>
       <c r="C6" t="n">
-        <v>6678</v>
+        <v>6855</v>
       </c>
       <c r="D6" t="n">
-        <v>2048</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>654</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>5231</v>
+        <v>5356</v>
       </c>
       <c r="D7" t="n">
-        <v>823</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>3054</v>
+        <v>3070</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1268</v>
+        <v>1195</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5325</v>
+        <v>5540</v>
       </c>
       <c r="C2" t="n">
-        <v>7439</v>
+        <v>10272</v>
       </c>
       <c r="D2" t="n">
-        <v>4290</v>
+        <v>15215</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3489</v>
+        <v>2621</v>
       </c>
       <c r="C2" t="n">
-        <v>2313</v>
+        <v>3745</v>
       </c>
       <c r="D2" t="n">
-        <v>7678</v>
+        <v>11238</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3737</v>
+        <v>3166</v>
       </c>
       <c r="C3" t="n">
-        <v>3907</v>
+        <v>4174</v>
       </c>
       <c r="D3" t="n">
-        <v>10699</v>
+        <v>14877</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3986</v>
+        <v>3548</v>
       </c>
       <c r="C4" t="n">
-        <v>6979</v>
+        <v>6787</v>
       </c>
       <c r="D4" t="n">
-        <v>8811</v>
+        <v>13084</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1740</v>
+        <v>1521</v>
       </c>
       <c r="C5" t="n">
-        <v>9247</v>
+        <v>9385</v>
       </c>
       <c r="D5" t="n">
-        <v>4563</v>
+        <v>6576</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>604</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>6566</v>
+        <v>6592</v>
       </c>
       <c r="D6" t="n">
-        <v>1697</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2992</v>
+        <v>3008</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1242</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6516</v>
+        <v>7192</v>
       </c>
       <c r="C2" t="n">
-        <v>3692</v>
+        <v>5879</v>
       </c>
       <c r="D2" t="n">
-        <v>9078</v>
+        <v>27356</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2263</v>
+        <v>2354</v>
       </c>
       <c r="C3" t="n">
-        <v>3808</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="n">
-        <v>1394</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4848</v>
+        <v>4420</v>
       </c>
       <c r="C2" t="n">
-        <v>5605</v>
+        <v>5768</v>
       </c>
       <c r="D2" t="n">
-        <v>10084</v>
+        <v>31129</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3603</v>
+        <v>3917</v>
       </c>
       <c r="C3" t="n">
-        <v>3220</v>
+        <v>4807</v>
       </c>
       <c r="D3" t="n">
-        <v>2582</v>
+        <v>7018</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1016</v>
+        <v>1057</v>
       </c>
       <c r="C4" t="n">
-        <v>2310</v>
+        <v>3077</v>
       </c>
       <c r="D4" t="n">
-        <v>1462</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4827</v>
+        <v>5299</v>
       </c>
       <c r="C2" t="n">
-        <v>7227</v>
+        <v>5523</v>
       </c>
       <c r="D2" t="n">
-        <v>11464</v>
+        <v>24884</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3504</v>
+        <v>3432</v>
       </c>
       <c r="C3" t="n">
-        <v>3912</v>
+        <v>4614</v>
       </c>
       <c r="D3" t="n">
-        <v>3596</v>
+        <v>10370</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1954</v>
+        <v>2079</v>
       </c>
       <c r="C4" t="n">
-        <v>2755</v>
+        <v>3976</v>
       </c>
       <c r="D4" t="n">
-        <v>1618</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="C5" t="n">
-        <v>1379</v>
+        <v>1751</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5864</v>
+        <v>6159</v>
       </c>
       <c r="C2" t="n">
-        <v>4150</v>
+        <v>4974</v>
       </c>
       <c r="D2" t="n">
-        <v>19117</v>
+        <v>26511</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3397</v>
+        <v>3529</v>
       </c>
       <c r="C3" t="n">
-        <v>4910</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>4538</v>
+        <v>11846</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2302</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>3330</v>
+        <v>4230</v>
       </c>
       <c r="D4" t="n">
-        <v>1914</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1012</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="n">
-        <v>2063</v>
+        <v>2829</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7605</v>
+        <v>6826</v>
       </c>
       <c r="C2" t="n">
-        <v>5033</v>
+        <v>9270</v>
       </c>
       <c r="D2" t="n">
-        <v>24148</v>
+        <v>27095</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3357</v>
+        <v>3464</v>
       </c>
       <c r="C3" t="n">
-        <v>3695</v>
+        <v>3852</v>
       </c>
       <c r="D3" t="n">
-        <v>6052</v>
+        <v>12458</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1768</v>
+        <v>1797</v>
       </c>
       <c r="C4" t="n">
-        <v>3458</v>
+        <v>3545</v>
       </c>
       <c r="D4" t="n">
-        <v>2019</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>1982</v>
+        <v>2562</v>
       </c>
       <c r="D5" t="n">
-        <v>1075</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>995</v>
+        <v>1290</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5352</v>
+        <v>6645</v>
       </c>
       <c r="C2" t="n">
-        <v>8819</v>
+        <v>8853</v>
       </c>
       <c r="D2" t="n">
-        <v>22888</v>
+        <v>25201</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4601</v>
+        <v>4256</v>
       </c>
       <c r="C3" t="n">
-        <v>3858</v>
+        <v>6003</v>
       </c>
       <c r="D3" t="n">
-        <v>8781</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2267</v>
+        <v>2300</v>
       </c>
       <c r="C4" t="n">
-        <v>3533</v>
+        <v>3619</v>
       </c>
       <c r="D4" t="n">
-        <v>2809</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C5" t="n">
-        <v>2833</v>
+        <v>3084</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C6" t="n">
-        <v>1560</v>
+        <v>1994</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>737</v>
+        <v>909</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4454</v>
+        <v>4800</v>
       </c>
       <c r="C2" t="n">
-        <v>5037</v>
+        <v>6175</v>
       </c>
       <c r="D2" t="n">
-        <v>18825</v>
+        <v>21628</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4104</v>
+        <v>4437</v>
       </c>
       <c r="C3" t="n">
-        <v>5748</v>
+        <v>6528</v>
       </c>
       <c r="D3" t="n">
-        <v>10504</v>
+        <v>14784</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2984</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>3649</v>
+        <v>4871</v>
       </c>
       <c r="D4" t="n">
-        <v>3927</v>
+        <v>7435</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="C5" t="n">
-        <v>3170</v>
+        <v>3307</v>
       </c>
       <c r="D5" t="n">
-        <v>1489</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>2238</v>
+        <v>2517</v>
       </c>
       <c r="D6" t="n">
-        <v>858</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>1173</v>
+        <v>1472</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>537</v>
+        <v>620</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_65_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7534</v>
+        <v>4945</v>
       </c>
       <c r="C2" t="n">
-        <v>6039</v>
+        <v>4799</v>
       </c>
       <c r="D2" t="n">
-        <v>30411</v>
+        <v>24970</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3844</v>
+        <v>3180</v>
       </c>
       <c r="C3" t="n">
-        <v>5563</v>
+        <v>6224</v>
       </c>
       <c r="D3" t="n">
-        <v>14752</v>
+        <v>13862</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3012</v>
+        <v>2845</v>
       </c>
       <c r="C4" t="n">
-        <v>5566</v>
+        <v>5652</v>
       </c>
       <c r="D4" t="n">
-        <v>8407</v>
+        <v>7189</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1831</v>
+        <v>1898</v>
       </c>
       <c r="C5" t="n">
-        <v>4018</v>
+        <v>4846</v>
       </c>
       <c r="D5" t="n">
-        <v>3464</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>2845</v>
+        <v>3183</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>1856</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>1012</v>
+        <v>845</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7333</v>
+        <v>6852</v>
       </c>
       <c r="C2" t="n">
-        <v>7809</v>
+        <v>5395</v>
       </c>
       <c r="D2" t="n">
-        <v>34116</v>
+        <v>35095</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4403</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>5090</v>
+        <v>4907</v>
       </c>
       <c r="D3" t="n">
-        <v>15890</v>
+        <v>14441</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2908</v>
+        <v>2565</v>
       </c>
       <c r="C4" t="n">
-        <v>5448</v>
+        <v>5808</v>
       </c>
       <c r="D4" t="n">
-        <v>9186</v>
+        <v>8059</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="C5" t="n">
-        <v>4594</v>
+        <v>5070</v>
       </c>
       <c r="D5" t="n">
-        <v>4084</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>1267</v>
       </c>
       <c r="C6" t="n">
-        <v>3335</v>
+        <v>3902</v>
       </c>
       <c r="D6" t="n">
-        <v>1653</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C7" t="n">
-        <v>2328</v>
+        <v>2422</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C8" t="n">
-        <v>1406</v>
+        <v>1280</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7653</v>
+        <v>7258</v>
       </c>
       <c r="C2" t="n">
-        <v>10570</v>
+        <v>5223</v>
       </c>
       <c r="D2" t="n">
-        <v>29568</v>
+        <v>32665</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>3783</v>
+      </c>
+      <c r="C3" t="n">
         <v>4533</v>
       </c>
-      <c r="C3" t="n">
-        <v>5547</v>
-      </c>
       <c r="D3" t="n">
-        <v>17060</v>
+        <v>15995</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2973</v>
+        <v>2441</v>
       </c>
       <c r="C4" t="n">
-        <v>5131</v>
+        <v>5242</v>
       </c>
       <c r="D4" t="n">
-        <v>9783</v>
+        <v>8655</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2122</v>
+        <v>2011</v>
       </c>
       <c r="C5" t="n">
-        <v>4806</v>
+        <v>5227</v>
       </c>
       <c r="D5" t="n">
-        <v>4694</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1414</v>
+        <v>1432</v>
       </c>
       <c r="C6" t="n">
-        <v>3813</v>
+        <v>4349</v>
       </c>
       <c r="D6" t="n">
-        <v>1942</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C7" t="n">
-        <v>2698</v>
+        <v>2991</v>
       </c>
       <c r="D7" t="n">
-        <v>874</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C8" t="n">
-        <v>1744</v>
+        <v>1727</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>938</v>
+        <v>821</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7135</v>
+        <v>6653</v>
       </c>
       <c r="C2" t="n">
-        <v>7272</v>
+        <v>3551</v>
       </c>
       <c r="D2" t="n">
-        <v>24473</v>
+        <v>26899</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5390</v>
+        <v>4464</v>
       </c>
       <c r="C3" t="n">
-        <v>8627</v>
+        <v>7142</v>
       </c>
       <c r="D3" t="n">
-        <v>18564</v>
+        <v>17246</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1960</v>
+        <v>1858</v>
       </c>
       <c r="C4" t="n">
-        <v>7421</v>
+        <v>7886</v>
       </c>
       <c r="D4" t="n">
-        <v>9630</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>1323</v>
       </c>
       <c r="C5" t="n">
-        <v>3736</v>
+        <v>4262</v>
       </c>
       <c r="D5" t="n">
-        <v>3164</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>2644</v>
+        <v>2931</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>1709</v>
+        <v>1692</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>919</v>
+        <v>804</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>366</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4304</v>
+        <v>4051</v>
       </c>
       <c r="C2" t="n">
-        <v>3588</v>
+        <v>2219</v>
       </c>
       <c r="D2" t="n">
-        <v>17995</v>
+        <v>18467</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5314</v>
+        <v>4639</v>
       </c>
       <c r="C3" t="n">
-        <v>7273</v>
+        <v>4973</v>
       </c>
       <c r="D3" t="n">
-        <v>18476</v>
+        <v>17565</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>2480</v>
       </c>
       <c r="C4" t="n">
-        <v>8107</v>
+        <v>7674</v>
       </c>
       <c r="D4" t="n">
-        <v>10716</v>
+        <v>9617</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1467</v>
+        <v>1447</v>
       </c>
       <c r="C5" t="n">
-        <v>5323</v>
+        <v>5873</v>
       </c>
       <c r="D5" t="n">
-        <v>3935</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="C6" t="n">
-        <v>3146</v>
+        <v>3541</v>
       </c>
       <c r="D6" t="n">
-        <v>1092</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>2106</v>
+        <v>2180</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>1173</v>
+        <v>1063</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>422</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>3828</v>
       </c>
       <c r="C2" t="n">
-        <v>6835</v>
+        <v>5223</v>
       </c>
       <c r="D2" t="n">
-        <v>16524</v>
+        <v>16790</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4117</v>
+        <v>3685</v>
       </c>
       <c r="C3" t="n">
-        <v>4885</v>
+        <v>3214</v>
       </c>
       <c r="D3" t="n">
-        <v>17168</v>
+        <v>16655</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3342</v>
+        <v>2948</v>
       </c>
       <c r="C4" t="n">
-        <v>7530</v>
+        <v>6239</v>
       </c>
       <c r="D4" t="n">
-        <v>11656</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1791</v>
+        <v>1679</v>
       </c>
       <c r="C5" t="n">
-        <v>6572</v>
+        <v>6598</v>
       </c>
       <c r="D5" t="n">
-        <v>4856</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>4077</v>
+        <v>4593</v>
       </c>
       <c r="D6" t="n">
-        <v>1486</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>2574</v>
+        <v>2765</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>1558</v>
+        <v>1532</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>729</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2828</v>
+        <v>2286</v>
       </c>
       <c r="C2" t="n">
-        <v>3204</v>
+        <v>2407</v>
       </c>
       <c r="D2" t="n">
-        <v>11584</v>
+        <v>11598</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4158</v>
+        <v>3588</v>
       </c>
       <c r="C3" t="n">
-        <v>5391</v>
+        <v>3802</v>
       </c>
       <c r="D3" t="n">
-        <v>16716</v>
+        <v>16270</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3634</v>
+        <v>3261</v>
       </c>
       <c r="C4" t="n">
-        <v>7232</v>
+        <v>5751</v>
       </c>
       <c r="D4" t="n">
-        <v>12383</v>
+        <v>11528</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1847</v>
+        <v>1766</v>
       </c>
       <c r="C5" t="n">
-        <v>7823</v>
+        <v>7496</v>
       </c>
       <c r="D5" t="n">
-        <v>5111</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="C6" t="n">
-        <v>4903</v>
+        <v>5523</v>
       </c>
       <c r="D6" t="n">
-        <v>1444</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>2863</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1187</v>
+        <v>1141</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3623</v>
+        <v>2874</v>
       </c>
       <c r="C2" t="n">
-        <v>5248</v>
+        <v>3172</v>
       </c>
       <c r="D2" t="n">
-        <v>18300</v>
+        <v>15446</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3088</v>
+        <v>2602</v>
       </c>
       <c r="C3" t="n">
-        <v>3921</v>
+        <v>2807</v>
       </c>
       <c r="D3" t="n">
-        <v>15055</v>
+        <v>14541</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3363</v>
+        <v>3000</v>
       </c>
       <c r="C4" t="n">
-        <v>6284</v>
+        <v>4751</v>
       </c>
       <c r="D4" t="n">
-        <v>12672</v>
+        <v>11951</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2292</v>
+        <v>2109</v>
       </c>
       <c r="C5" t="n">
-        <v>7399</v>
+        <v>6552</v>
       </c>
       <c r="D5" t="n">
-        <v>6002</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="C6" t="n">
-        <v>6187</v>
+        <v>6431</v>
       </c>
       <c r="D6" t="n">
-        <v>1918</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>3615</v>
+        <v>3958</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1773</v>
+        <v>1815</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2675</v>
+        <v>2035</v>
       </c>
       <c r="C2" t="n">
-        <v>2784</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="n">
-        <v>13806</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2856</v>
+        <v>2357</v>
       </c>
       <c r="C3" t="n">
-        <v>4030</v>
+        <v>2703</v>
       </c>
       <c r="D3" t="n">
-        <v>14625</v>
+        <v>13858</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3024</v>
+        <v>2655</v>
       </c>
       <c r="C4" t="n">
-        <v>5381</v>
+        <v>3986</v>
       </c>
       <c r="D4" t="n">
-        <v>12850</v>
+        <v>12050</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2472</v>
+        <v>2263</v>
       </c>
       <c r="C5" t="n">
-        <v>7062</v>
+        <v>5947</v>
       </c>
       <c r="D5" t="n">
-        <v>6581</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1302</v>
+        <v>1279</v>
       </c>
       <c r="C6" t="n">
-        <v>6820</v>
+        <v>6739</v>
       </c>
       <c r="D6" t="n">
-        <v>2304</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>4491</v>
+        <v>4858</v>
       </c>
       <c r="D7" t="n">
-        <v>789</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2264</v>
+        <v>2371</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3664</v>
+        <v>3909</v>
       </c>
       <c r="C2" t="n">
-        <v>6501</v>
+        <v>4526</v>
       </c>
       <c r="D2" t="n">
-        <v>15268</v>
+        <v>23515</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2349</v>
+        <v>1883</v>
       </c>
       <c r="C3" t="n">
-        <v>3146</v>
+        <v>2172</v>
       </c>
       <c r="D3" t="n">
-        <v>13590</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2602</v>
+        <v>2235</v>
       </c>
       <c r="C4" t="n">
-        <v>4698</v>
+        <v>3348</v>
       </c>
       <c r="D4" t="n">
-        <v>12714</v>
+        <v>11828</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2426</v>
+        <v>2190</v>
       </c>
       <c r="C5" t="n">
-        <v>6237</v>
+        <v>5013</v>
       </c>
       <c r="D5" t="n">
-        <v>7223</v>
+        <v>6751</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1574</v>
+        <v>1508</v>
       </c>
       <c r="C6" t="n">
-        <v>6855</v>
+        <v>6369</v>
       </c>
       <c r="D6" t="n">
-        <v>2808</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="C7" t="n">
-        <v>5356</v>
+        <v>5574</v>
       </c>
       <c r="D7" t="n">
-        <v>959</v>
+        <v>896</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>3070</v>
+        <v>3295</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1195</v>
+        <v>1243</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5540</v>
+        <v>5007</v>
       </c>
       <c r="C2" t="n">
-        <v>10272</v>
+        <v>6985</v>
       </c>
       <c r="D2" t="n">
-        <v>15215</v>
+        <v>7696</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2621</v>
+        <v>2763</v>
       </c>
       <c r="C2" t="n">
-        <v>3745</v>
+        <v>2534</v>
       </c>
       <c r="D2" t="n">
-        <v>11238</v>
+        <v>17307</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3166</v>
+        <v>2684</v>
       </c>
       <c r="C3" t="n">
-        <v>4174</v>
+        <v>2921</v>
       </c>
       <c r="D3" t="n">
-        <v>14877</v>
+        <v>14510</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3548</v>
+        <v>3142</v>
       </c>
       <c r="C4" t="n">
-        <v>6787</v>
+        <v>4956</v>
       </c>
       <c r="D4" t="n">
-        <v>13084</v>
+        <v>12115</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1521</v>
+        <v>1474</v>
       </c>
       <c r="C5" t="n">
-        <v>9385</v>
+        <v>8251</v>
       </c>
       <c r="D5" t="n">
-        <v>6576</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C6" t="n">
-        <v>6592</v>
+        <v>6773</v>
       </c>
       <c r="D6" t="n">
-        <v>2193</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>3008</v>
+        <v>3229</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1171</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7192</v>
+        <v>6257</v>
       </c>
       <c r="C2" t="n">
-        <v>5879</v>
+        <v>4502</v>
       </c>
       <c r="D2" t="n">
-        <v>27356</v>
+        <v>11862</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2354</v>
+        <v>2128</v>
       </c>
       <c r="C3" t="n">
-        <v>5177</v>
+        <v>3520</v>
       </c>
       <c r="D3" t="n">
-        <v>3195</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4420</v>
+        <v>4528</v>
       </c>
       <c r="C2" t="n">
-        <v>5768</v>
+        <v>8739</v>
       </c>
       <c r="D2" t="n">
-        <v>31129</v>
+        <v>28603</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3917</v>
+        <v>3441</v>
       </c>
       <c r="C3" t="n">
-        <v>4807</v>
+        <v>3517</v>
       </c>
       <c r="D3" t="n">
-        <v>7018</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1057</v>
+        <v>958</v>
       </c>
       <c r="C4" t="n">
-        <v>3077</v>
+        <v>2138</v>
       </c>
       <c r="D4" t="n">
-        <v>1825</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5299</v>
+        <v>5832</v>
       </c>
       <c r="C2" t="n">
-        <v>5523</v>
+        <v>8046</v>
       </c>
       <c r="D2" t="n">
-        <v>24884</v>
+        <v>23454</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3432</v>
+        <v>3270</v>
       </c>
       <c r="C3" t="n">
-        <v>4614</v>
+        <v>5509</v>
       </c>
       <c r="D3" t="n">
-        <v>10370</v>
+        <v>7232</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2079</v>
+        <v>1860</v>
       </c>
       <c r="C4" t="n">
-        <v>3976</v>
+        <v>2874</v>
       </c>
       <c r="D4" t="n">
-        <v>2766</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C5" t="n">
-        <v>1751</v>
+        <v>1264</v>
       </c>
       <c r="D5" t="n">
-        <v>1275</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6159</v>
+        <v>6126</v>
       </c>
       <c r="C2" t="n">
-        <v>4974</v>
+        <v>5579</v>
       </c>
       <c r="D2" t="n">
-        <v>26511</v>
+        <v>26832</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3529</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>5931</v>
       </c>
       <c r="D3" t="n">
-        <v>11846</v>
+        <v>9188</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>2181</v>
       </c>
       <c r="C4" t="n">
         <v>4230</v>
       </c>
       <c r="D4" t="n">
-        <v>4068</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1035</v>
+        <v>948</v>
       </c>
       <c r="C5" t="n">
-        <v>2829</v>
+        <v>2060</v>
       </c>
       <c r="D5" t="n">
-        <v>1481</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>1024</v>
+        <v>787</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
         <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6826</v>
+        <v>7007</v>
       </c>
       <c r="C2" t="n">
-        <v>9270</v>
+        <v>11041</v>
       </c>
       <c r="D2" t="n">
-        <v>27095</v>
+        <v>29924</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3464</v>
+        <v>3530</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>4711</v>
       </c>
       <c r="D3" t="n">
-        <v>12458</v>
+        <v>10558</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="C4" t="n">
-        <v>3545</v>
+        <v>4233</v>
       </c>
       <c r="D4" t="n">
-        <v>4679</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>871</v>
+        <v>819</v>
       </c>
       <c r="C5" t="n">
-        <v>2562</v>
+        <v>2314</v>
       </c>
       <c r="D5" t="n">
-        <v>1513</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C6" t="n">
-        <v>1290</v>
+        <v>962</v>
       </c>
       <c r="D6" t="n">
-        <v>791</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>428</v>
+        <v>359</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6645</v>
+        <v>4904</v>
       </c>
       <c r="C2" t="n">
-        <v>8853</v>
+        <v>6133</v>
       </c>
       <c r="D2" t="n">
-        <v>25201</v>
+        <v>22268</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4256</v>
+        <v>4384</v>
       </c>
       <c r="C3" t="n">
-        <v>6003</v>
+        <v>7238</v>
       </c>
       <c r="D3" t="n">
-        <v>14000</v>
+        <v>13034</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2300</v>
+        <v>2345</v>
       </c>
       <c r="C4" t="n">
-        <v>3619</v>
+        <v>4434</v>
       </c>
       <c r="D4" t="n">
-        <v>6105</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="C5" t="n">
-        <v>3084</v>
+        <v>3389</v>
       </c>
       <c r="D5" t="n">
-        <v>2060</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="C6" t="n">
-        <v>1994</v>
+        <v>1706</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>909</v>
+        <v>701</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4800</v>
+        <v>3854</v>
       </c>
       <c r="C2" t="n">
-        <v>6175</v>
+        <v>8539</v>
       </c>
       <c r="D2" t="n">
-        <v>21628</v>
+        <v>22073</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4437</v>
+        <v>3827</v>
       </c>
       <c r="C3" t="n">
-        <v>6528</v>
+        <v>5743</v>
       </c>
       <c r="D3" t="n">
-        <v>14784</v>
+        <v>13572</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>2889</v>
       </c>
       <c r="C4" t="n">
-        <v>4871</v>
+        <v>5929</v>
       </c>
       <c r="D4" t="n">
-        <v>7435</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="C5" t="n">
-        <v>3307</v>
+        <v>3890</v>
       </c>
       <c r="D5" t="n">
-        <v>2735</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="C6" t="n">
-        <v>2517</v>
+        <v>2558</v>
       </c>
       <c r="D6" t="n">
-        <v>1093</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>1472</v>
+        <v>1232</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>620</v>
+        <v>502</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_65_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4945</v>
+        <v>1232</v>
       </c>
       <c r="C2" t="n">
-        <v>4799</v>
+        <v>3103</v>
       </c>
       <c r="D2" t="n">
-        <v>24970</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3180</v>
+        <v>2061</v>
       </c>
       <c r="C3" t="n">
-        <v>6224</v>
+        <v>7540</v>
       </c>
       <c r="D3" t="n">
-        <v>13862</v>
+        <v>17494</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2845</v>
+        <v>1651</v>
       </c>
       <c r="C4" t="n">
-        <v>5652</v>
+        <v>8916</v>
       </c>
       <c r="D4" t="n">
-        <v>7189</v>
+        <v>6936</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>964</v>
       </c>
       <c r="C5" t="n">
-        <v>4846</v>
+        <v>5222</v>
       </c>
       <c r="D5" t="n">
-        <v>2742</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>379</v>
       </c>
       <c r="C6" t="n">
-        <v>3183</v>
+        <v>2173</v>
       </c>
       <c r="D6" t="n">
-        <v>1128</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1856</v>
+        <v>724</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>845</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6852</v>
+        <v>1182</v>
       </c>
       <c r="C2" t="n">
-        <v>5395</v>
+        <v>10820</v>
       </c>
       <c r="D2" t="n">
-        <v>35095</v>
+        <v>21342</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>1419</v>
       </c>
       <c r="C3" t="n">
-        <v>4907</v>
+        <v>4647</v>
       </c>
       <c r="D3" t="n">
-        <v>14441</v>
+        <v>17246</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2565</v>
+        <v>1606</v>
       </c>
       <c r="C4" t="n">
-        <v>5808</v>
+        <v>8004</v>
       </c>
       <c r="D4" t="n">
-        <v>8059</v>
+        <v>8650</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2039</v>
+        <v>1134</v>
       </c>
       <c r="C5" t="n">
-        <v>5070</v>
+        <v>7043</v>
       </c>
       <c r="D5" t="n">
-        <v>3315</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1267</v>
+        <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>3902</v>
+        <v>3635</v>
       </c>
       <c r="D6" t="n">
-        <v>1360</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>610</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>2422</v>
+        <v>1398</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>512</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>558</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7258</v>
+        <v>651</v>
       </c>
       <c r="C2" t="n">
-        <v>5223</v>
+        <v>4710</v>
       </c>
       <c r="D2" t="n">
-        <v>32665</v>
+        <v>14527</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3783</v>
+        <v>1306</v>
       </c>
       <c r="C3" t="n">
-        <v>4533</v>
+        <v>6703</v>
       </c>
       <c r="D3" t="n">
-        <v>15995</v>
+        <v>17296</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2441</v>
+        <v>1751</v>
       </c>
       <c r="C4" t="n">
-        <v>5242</v>
+        <v>7425</v>
       </c>
       <c r="D4" t="n">
-        <v>8655</v>
+        <v>9709</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2011</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="n">
-        <v>5227</v>
+        <v>8221</v>
       </c>
       <c r="D5" t="n">
-        <v>3897</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1432</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>4349</v>
+        <v>4496</v>
       </c>
       <c r="D6" t="n">
-        <v>1591</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>775</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2991</v>
+        <v>1303</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1727</v>
+        <v>475</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>821</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6653</v>
+        <v>1175</v>
       </c>
       <c r="C2" t="n">
-        <v>3551</v>
+        <v>5861</v>
       </c>
       <c r="D2" t="n">
-        <v>26899</v>
+        <v>15564</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4464</v>
+        <v>874</v>
       </c>
       <c r="C3" t="n">
-        <v>7142</v>
+        <v>5059</v>
       </c>
       <c r="D3" t="n">
-        <v>17246</v>
+        <v>15707</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1858</v>
+        <v>1392</v>
       </c>
       <c r="C4" t="n">
-        <v>7886</v>
+        <v>6974</v>
       </c>
       <c r="D4" t="n">
-        <v>8343</v>
+        <v>10818</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1323</v>
+        <v>1268</v>
       </c>
       <c r="C5" t="n">
-        <v>4262</v>
+        <v>7746</v>
       </c>
       <c r="D5" t="n">
-        <v>2606</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>640</v>
       </c>
       <c r="C6" t="n">
-        <v>2931</v>
+        <v>6220</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1692</v>
+        <v>2673</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4051</v>
+        <v>659</v>
       </c>
       <c r="C2" t="n">
-        <v>2219</v>
+        <v>3567</v>
       </c>
       <c r="D2" t="n">
-        <v>18467</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4639</v>
+        <v>856</v>
       </c>
       <c r="C3" t="n">
-        <v>4973</v>
+        <v>4873</v>
       </c>
       <c r="D3" t="n">
-        <v>17565</v>
+        <v>14809</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2480</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="n">
-        <v>7674</v>
+        <v>6184</v>
       </c>
       <c r="D4" t="n">
-        <v>9617</v>
+        <v>11297</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1447</v>
+        <v>1292</v>
       </c>
       <c r="C5" t="n">
-        <v>5873</v>
+        <v>7578</v>
       </c>
       <c r="D5" t="n">
-        <v>3292</v>
+        <v>4933</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>758</v>
       </c>
       <c r="C6" t="n">
-        <v>3541</v>
+        <v>6991</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>2180</v>
+        <v>3828</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>1233</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3828</v>
+        <v>1647</v>
       </c>
       <c r="C2" t="n">
-        <v>5223</v>
+        <v>9311</v>
       </c>
       <c r="D2" t="n">
-        <v>16790</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3685</v>
+        <v>655</v>
       </c>
       <c r="C3" t="n">
-        <v>3214</v>
+        <v>3849</v>
       </c>
       <c r="D3" t="n">
-        <v>16655</v>
+        <v>13491</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2948</v>
+        <v>903</v>
       </c>
       <c r="C4" t="n">
-        <v>6239</v>
+        <v>5463</v>
       </c>
       <c r="D4" t="n">
-        <v>10621</v>
+        <v>11493</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1679</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>6598</v>
+        <v>6818</v>
       </c>
       <c r="D5" t="n">
-        <v>4131</v>
+        <v>5699</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>4593</v>
+        <v>7170</v>
       </c>
       <c r="D6" t="n">
-        <v>1307</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>2765</v>
+        <v>5134</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1532</v>
+        <v>2198</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>704</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>173</v>
+      </c>
+      <c r="D11" t="n">
         <v>189</v>
-      </c>
-      <c r="D11" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2286</v>
+        <v>1146</v>
       </c>
       <c r="C2" t="n">
-        <v>2407</v>
+        <v>5065</v>
       </c>
       <c r="D2" t="n">
-        <v>11598</v>
+        <v>11717</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3588</v>
+        <v>998</v>
       </c>
       <c r="C3" t="n">
-        <v>3802</v>
+        <v>5561</v>
       </c>
       <c r="D3" t="n">
-        <v>16270</v>
+        <v>14772</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3261</v>
+        <v>1506</v>
       </c>
       <c r="C4" t="n">
-        <v>5751</v>
+        <v>7725</v>
       </c>
       <c r="D4" t="n">
-        <v>11528</v>
+        <v>11684</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>863</v>
       </c>
       <c r="C5" t="n">
-        <v>7496</v>
+        <v>10062</v>
       </c>
       <c r="D5" t="n">
-        <v>4372</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>836</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>5523</v>
+        <v>6577</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2863</v>
+        <v>2154</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1141</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
+        <v>169</v>
+      </c>
+      <c r="D10" t="n">
         <v>185</v>
-      </c>
-      <c r="D10" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2874</v>
+        <v>579</v>
       </c>
       <c r="C2" t="n">
-        <v>3172</v>
+        <v>3984</v>
       </c>
       <c r="D2" t="n">
-        <v>15446</v>
+        <v>9144</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2602</v>
+        <v>886</v>
       </c>
       <c r="C3" t="n">
-        <v>2807</v>
+        <v>4717</v>
       </c>
       <c r="D3" t="n">
-        <v>14541</v>
+        <v>13319</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
+        <v>1059</v>
       </c>
       <c r="C4" t="n">
-        <v>4751</v>
+        <v>6258</v>
       </c>
       <c r="D4" t="n">
-        <v>11951</v>
+        <v>11337</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2109</v>
+        <v>801</v>
       </c>
       <c r="C5" t="n">
-        <v>6552</v>
+        <v>7980</v>
       </c>
       <c r="D5" t="n">
-        <v>5380</v>
+        <v>5367</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1078</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>6431</v>
+        <v>6545</v>
       </c>
       <c r="D6" t="n">
-        <v>1678</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>3958</v>
+        <v>2832</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1815</v>
+        <v>794</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>254</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2035</v>
+        <v>496</v>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>8333</v>
       </c>
       <c r="D2" t="n">
-        <v>11027</v>
+        <v>16742</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2357</v>
+        <v>628</v>
       </c>
       <c r="C3" t="n">
-        <v>2703</v>
+        <v>3777</v>
       </c>
       <c r="D3" t="n">
-        <v>13858</v>
+        <v>11746</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2655</v>
+        <v>853</v>
       </c>
       <c r="C4" t="n">
-        <v>3986</v>
+        <v>5359</v>
       </c>
       <c r="D4" t="n">
-        <v>12050</v>
+        <v>11353</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2263</v>
+        <v>832</v>
       </c>
       <c r="C5" t="n">
-        <v>5947</v>
+        <v>6937</v>
       </c>
       <c r="D5" t="n">
-        <v>6076</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1279</v>
+        <v>469</v>
       </c>
       <c r="C6" t="n">
-        <v>6739</v>
+        <v>7242</v>
       </c>
       <c r="D6" t="n">
-        <v>2010</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>4858</v>
+        <v>4577</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>2371</v>
+        <v>1720</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>670</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3909</v>
+        <v>710</v>
       </c>
       <c r="C2" t="n">
-        <v>4526</v>
+        <v>15513</v>
       </c>
       <c r="D2" t="n">
-        <v>23515</v>
+        <v>23647</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1883</v>
+        <v>476</v>
       </c>
       <c r="C3" t="n">
-        <v>2172</v>
+        <v>5212</v>
       </c>
       <c r="D3" t="n">
-        <v>12719</v>
+        <v>11636</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2235</v>
+        <v>660</v>
       </c>
       <c r="C4" t="n">
-        <v>3348</v>
+        <v>4436</v>
       </c>
       <c r="D4" t="n">
-        <v>11828</v>
+        <v>11072</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2190</v>
+        <v>767</v>
       </c>
       <c r="C5" t="n">
-        <v>5013</v>
+        <v>6050</v>
       </c>
       <c r="D5" t="n">
-        <v>6751</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1508</v>
+        <v>565</v>
       </c>
       <c r="C6" t="n">
-        <v>6369</v>
+        <v>7033</v>
       </c>
       <c r="D6" t="n">
-        <v>2530</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>545</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>5574</v>
+        <v>5750</v>
       </c>
       <c r="D7" t="n">
-        <v>896</v>
+        <v>980</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>3295</v>
+        <v>2923</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1243</v>
+        <v>975</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>365</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5007</v>
+        <v>6967</v>
       </c>
       <c r="C2" t="n">
-        <v>6985</v>
+        <v>10277</v>
       </c>
       <c r="D2" t="n">
-        <v>7696</v>
+        <v>18810</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2763</v>
+        <v>1256</v>
       </c>
       <c r="C2" t="n">
-        <v>2534</v>
+        <v>16747</v>
       </c>
       <c r="D2" t="n">
-        <v>17307</v>
+        <v>22629</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2684</v>
+        <v>471</v>
       </c>
       <c r="C3" t="n">
-        <v>2921</v>
+        <v>8336</v>
       </c>
       <c r="D3" t="n">
-        <v>14510</v>
+        <v>12332</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3142</v>
+        <v>509</v>
       </c>
       <c r="C4" t="n">
-        <v>4956</v>
+        <v>4636</v>
       </c>
       <c r="D4" t="n">
-        <v>12115</v>
+        <v>10710</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1474</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>8251</v>
+        <v>5242</v>
       </c>
       <c r="D5" t="n">
-        <v>6165</v>
+        <v>7184</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>503</v>
+        <v>597</v>
       </c>
       <c r="C6" t="n">
-        <v>6773</v>
+        <v>6505</v>
       </c>
       <c r="D6" t="n">
-        <v>2003</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>3229</v>
+        <v>6263</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>4002</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>1671</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>534</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6257</v>
+        <v>7319</v>
       </c>
       <c r="C2" t="n">
-        <v>4502</v>
+        <v>13164</v>
       </c>
       <c r="D2" t="n">
-        <v>11862</v>
+        <v>22898</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2128</v>
+        <v>2245</v>
       </c>
       <c r="C3" t="n">
-        <v>3520</v>
+        <v>4058</v>
       </c>
       <c r="D3" t="n">
-        <v>1932</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4528</v>
+        <v>3481</v>
       </c>
       <c r="C2" t="n">
-        <v>8739</v>
+        <v>5945</v>
       </c>
       <c r="D2" t="n">
-        <v>28603</v>
+        <v>17949</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3441</v>
+        <v>4041</v>
       </c>
       <c r="C3" t="n">
-        <v>3517</v>
+        <v>8142</v>
       </c>
       <c r="D3" t="n">
-        <v>3458</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>958</v>
+        <v>1062</v>
       </c>
       <c r="C4" t="n">
-        <v>2138</v>
+        <v>2542</v>
       </c>
       <c r="D4" t="n">
-        <v>1570</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5832</v>
+        <v>2968</v>
       </c>
       <c r="C2" t="n">
-        <v>8046</v>
+        <v>3613</v>
       </c>
       <c r="D2" t="n">
-        <v>23454</v>
+        <v>27773</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3270</v>
+        <v>3107</v>
       </c>
       <c r="C3" t="n">
-        <v>5509</v>
+        <v>5918</v>
       </c>
       <c r="D3" t="n">
-        <v>7232</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1860</v>
+        <v>2208</v>
       </c>
       <c r="C4" t="n">
-        <v>2874</v>
+        <v>5822</v>
       </c>
       <c r="D4" t="n">
-        <v>1884</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="C5" t="n">
-        <v>1264</v>
+        <v>1548</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6126</v>
+        <v>1940</v>
       </c>
       <c r="C2" t="n">
-        <v>5579</v>
+        <v>8249</v>
       </c>
       <c r="D2" t="n">
-        <v>26832</v>
+        <v>26080</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>2539</v>
       </c>
       <c r="C3" t="n">
-        <v>5931</v>
+        <v>4062</v>
       </c>
       <c r="D3" t="n">
-        <v>9188</v>
+        <v>10489</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2181</v>
+        <v>2267</v>
       </c>
       <c r="C4" t="n">
-        <v>4230</v>
+        <v>5754</v>
       </c>
       <c r="D4" t="n">
-        <v>2802</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>948</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="n">
-        <v>2060</v>
+        <v>3813</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>787</v>
+        <v>923</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7007</v>
+        <v>1702</v>
       </c>
       <c r="C2" t="n">
-        <v>11041</v>
+        <v>10888</v>
       </c>
       <c r="D2" t="n">
-        <v>29924</v>
+        <v>33966</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3530</v>
+        <v>1882</v>
       </c>
       <c r="C3" t="n">
-        <v>4711</v>
+        <v>5384</v>
       </c>
       <c r="D3" t="n">
-        <v>10558</v>
+        <v>12120</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1801</v>
+        <v>2076</v>
       </c>
       <c r="C4" t="n">
-        <v>4233</v>
+        <v>4740</v>
       </c>
       <c r="D4" t="n">
-        <v>3388</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>819</v>
+        <v>1459</v>
       </c>
       <c r="C5" t="n">
-        <v>2314</v>
+        <v>4721</v>
       </c>
       <c r="D5" t="n">
-        <v>1205</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>284</v>
+        <v>586</v>
       </c>
       <c r="C6" t="n">
-        <v>962</v>
+        <v>2328</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>359</v>
+        <v>593</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4904</v>
+        <v>2310</v>
       </c>
       <c r="C2" t="n">
-        <v>6133</v>
+        <v>10253</v>
       </c>
       <c r="D2" t="n">
-        <v>22268</v>
+        <v>43984</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4384</v>
+        <v>1515</v>
       </c>
       <c r="C3" t="n">
-        <v>7238</v>
+        <v>6974</v>
       </c>
       <c r="D3" t="n">
-        <v>13034</v>
+        <v>14276</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2345</v>
+        <v>1717</v>
       </c>
       <c r="C4" t="n">
-        <v>4434</v>
+        <v>4956</v>
       </c>
       <c r="D4" t="n">
-        <v>4697</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1168</v>
+        <v>1534</v>
       </c>
       <c r="C5" t="n">
-        <v>3389</v>
+        <v>4586</v>
       </c>
       <c r="D5" t="n">
-        <v>1608</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>507</v>
+        <v>874</v>
       </c>
       <c r="C6" t="n">
-        <v>1706</v>
+        <v>3407</v>
       </c>
       <c r="D6" t="n">
-        <v>837</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>701</v>
+        <v>1374</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>297</v>
+        <v>423</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3854</v>
+        <v>2119</v>
       </c>
       <c r="C2" t="n">
-        <v>8539</v>
+        <v>6479</v>
       </c>
       <c r="D2" t="n">
-        <v>22073</v>
+        <v>34894</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3827</v>
+        <v>2482</v>
       </c>
       <c r="C3" t="n">
-        <v>5743</v>
+        <v>10177</v>
       </c>
       <c r="D3" t="n">
-        <v>13572</v>
+        <v>15650</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2889</v>
+        <v>1417</v>
       </c>
       <c r="C4" t="n">
-        <v>5929</v>
+        <v>7399</v>
       </c>
       <c r="D4" t="n">
-        <v>6154</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1521</v>
+        <v>807</v>
       </c>
       <c r="C5" t="n">
-        <v>3890</v>
+        <v>3338</v>
       </c>
       <c r="D5" t="n">
-        <v>2107</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>758</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>2558</v>
+        <v>1346</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1232</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>502</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
